--- a/AAII_Financials/Yearly/BENF_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BENF_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="92">
   <si>
     <t>BENF</t>
   </si>
@@ -962,7 +962,7 @@
         <v>99000</v>
       </c>
       <c r="I17" s="3">
-        <v>118900</v>
+        <v>155200</v>
       </c>
       <c r="J17" s="3">
         <v>195700</v>
@@ -992,7 +992,7 @@
         <v>-43700</v>
       </c>
       <c r="I18" s="3">
-        <v>-14900</v>
+        <v>-51100</v>
       </c>
       <c r="J18" s="3">
         <v>-135400</v>
@@ -1035,8 +1035,8 @@
       <c r="H20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>4</v>
+      <c r="I20" s="3">
+        <v>-36300</v>
       </c>
       <c r="J20" s="3">
         <v>2100</v>
@@ -1395,8 +1395,8 @@
       <c r="H32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>4</v>
+      <c r="I32" s="3">
+        <v>36300</v>
       </c>
       <c r="J32" s="3">
         <v>-2100</v>
@@ -1636,7 +1636,7 @@
         <v>6500</v>
       </c>
       <c r="H43" s="3">
-        <v>4400</v>
+        <v>20700</v>
       </c>
       <c r="I43" s="3">
         <v>7000</v>
@@ -1726,7 +1726,7 @@
         <v>85000</v>
       </c>
       <c r="H46" s="3">
-        <v>27800</v>
+        <v>44100</v>
       </c>
       <c r="I46" s="3">
         <v>28000</v>
@@ -1906,7 +1906,7 @@
         <v>2400</v>
       </c>
       <c r="H52" s="3">
-        <v>18200</v>
+        <v>1900</v>
       </c>
       <c r="I52" s="3">
         <v>2000</v>
@@ -2024,7 +2024,7 @@
         <v>33500</v>
       </c>
       <c r="H57" s="3">
-        <v>38300</v>
+        <v>37000</v>
       </c>
       <c r="I57" s="3">
         <v>17800</v>
@@ -2084,7 +2084,7 @@
         <v>3800</v>
       </c>
       <c r="H59" s="3">
-        <v>20200</v>
+        <v>21500</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>4</v>
@@ -2147,7 +2147,7 @@
         <v>112100</v>
       </c>
       <c r="I61" s="3">
-        <v>256300</v>
+        <v>256600</v>
       </c>
       <c r="J61" s="3">
         <v>321800</v>
@@ -2177,7 +2177,7 @@
         <v>1500</v>
       </c>
       <c r="I62" s="3">
-        <v>1400</v>
+        <v>1100</v>
       </c>
       <c r="J62" s="3">
         <v>58500</v>
@@ -2717,10 +2717,10 @@
         <v>1500</v>
       </c>
       <c r="H83" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="I83" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="J83" s="3">
         <v>200</v>
